--- a/metadata/MIAFPE/MIAFPE_template_v0.1.xlsx
+++ b/metadata/MIAFPE/MIAFPE_template_v0.1.xlsx
@@ -15,7 +15,9 @@
     <sheet name="DataFile" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Location" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Institution" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Experimental Design" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="ExperimentalDesign" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Observation" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="ObservationUnit" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="333">
   <si>
     <t xml:space="preserve">Sheet Name</t>
   </si>
@@ -281,117 +283,123 @@
     <t xml:space="preserve">Location Metadata.</t>
   </si>
   <si>
+    <t xml:space="preserve">Location Unique Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unique Identifier which help to reference a certain location by a metadata internal ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experimental Site Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The name of the natural site, experimental field, greenhouse, phenotyping facility, etc. where the experiment took place.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The country where the experiment took place as a full name (In case of more than 1 use semicolon-separated format).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLASS: Country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hasCountry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The country where the experiment took place as a 2-letter code (In case of more than 1 use semicolon-separated format).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hasCountryCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latitude of the experimental site in degrees, in decimal format.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Degrees in the decimal format (ISO 6709)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hasLatitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exactly(1) if hasLongitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longitude of the experimental site in degrees, in decimal format.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hasLongitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exactly(1) if hasLatitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Altitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Altitude of the experimental site in degrees, in decimal format.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hasAltitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max(1) only if hasLatitude and hasLongitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth Facility Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short description of the facility in which the study was carried out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference to Controlled Vocabulary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLASS: GrowthFacility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hasGrowthFacility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth Facility Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type of growth facility in which the study was carried out, in the form of an accession number from the Crop Ontology.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hasGrowthFacilityType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth Facility External Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">External Identifier of the Growth Facility.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hasExternalIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spatial Reference Files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Files that can be linked to Location Properties.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Institution Metadata</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unique Identifier which acts as unambiguous link between Instances.</t>
   </si>
   <si>
-    <t xml:space="preserve">Experimental Site Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The name of the natural site, experimental field, greenhouse, phenotyping facility, etc. where the experiment took place.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The country where the experiment took place as a full name (In case of more than 1 use semicolon-separated format).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLASS: Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hasCountry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The country where the experiment took place as a 2-letter code (In case of more than 1 use semicolon-separated format).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hasCountryCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latitude of the experimental site in degrees, in decimal format.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Degrees in the decimal format (ISO 6709)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hasLatitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exactly(1) if hasLongitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitude of the experimental site in degrees, in decimal format.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hasLongitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exactly(1) if hasLatitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Altitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Altitude of the experimental site in degrees, in decimal format.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hasAltitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max(1) only if hasLatitude and hasLongitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Growth Facility Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Short description of the facility in which the study was carried out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference to Controlled Vocabulary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLASS: GrowthFacility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hasGrowthFacility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Growth Facility Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type of growth facility in which the study was carried out, in the form of an accession number from the Crop Ontology.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hasGrowthFacilityType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Growth Facility External Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External Identifier of the Growth Facility.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hasExternalIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spatial Reference Files</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Files that can be linked to Location Properties.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Institution Metadata</t>
-  </si>
-  <si>
     <t xml:space="preserve">Institution Name</t>
   </si>
   <si>
@@ -455,6 +463,9 @@
     <t xml:space="preserve">Experimental Design Metadata</t>
   </si>
   <si>
+    <t xml:space="preserve">Experimental Design ID</t>
+  </si>
+  <si>
     <t xml:space="preserve">Experimental Design Description</t>
   </si>
   <si>
@@ -927,6 +938,9 @@
   </si>
   <si>
     <t xml:space="preserve">A human involved in the investigation or specifically any of its studies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Person Unique Identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Person Name</t>
@@ -1020,10 +1034,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -1297,7 +1310,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1389,7 +1402,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1450,7 +1463,7 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
@@ -2295,10 +2308,10 @@
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7"/>
       <c r="B24" s="8" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9" t="s">
@@ -2328,10 +2341,10 @@
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7"/>
       <c r="B25" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>21</v>
@@ -2358,10 +2371,10 @@
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D26" s="27"/>
       <c r="E26" s="28" t="s">
@@ -2386,19 +2399,19 @@
       </c>
       <c r="K26" s="29"/>
       <c r="L26" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="27" t="s">
@@ -2408,7 +2421,7 @@
         <v>55</v>
       </c>
       <c r="G27" s="27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" s="27" t="s">
         <v>14</v>
@@ -2426,19 +2439,19 @@
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>14</v>
@@ -2452,25 +2465,25 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasLatitude</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>14</v>
@@ -2484,25 +2497,25 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasLongitude</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
       <c r="B30" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>14</v>
@@ -2516,16 +2529,16 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasAltitude</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
       <c r="B31" s="26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D31" s="27"/>
       <c r="E31" s="27" t="s">
@@ -2549,22 +2562,22 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasDescription</v>
       </c>
       <c r="K31" s="27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" s="30" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
       <c r="B32" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27" t="s">
@@ -2574,7 +2587,7 @@
         <v>13</v>
       </c>
       <c r="G32" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H32" s="27" t="s">
         <v>14</v>
@@ -2588,7 +2601,7 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#hasGrowthFacilityType</v>
       </c>
       <c r="K32" s="27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -2596,10 +2609,10 @@
     <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
       <c r="B33" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D33" s="27"/>
       <c r="E33" s="27" t="s">
@@ -2609,7 +2622,7 @@
         <v>25</v>
       </c>
       <c r="G33" s="27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H33" s="27" t="s">
         <v>14</v>
@@ -2627,10 +2640,10 @@
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D34" s="19"/>
       <c r="E34" s="17" t="s">
@@ -2661,7 +2674,7 @@
       </c>
       <c r="B35" s="21"/>
       <c r="C35" s="22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D35" s="22"/>
       <c r="E35" s="21"/>
@@ -2688,7 +2701,7 @@
         <v>17</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>17</v>
@@ -2717,10 +2730,10 @@
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="23"/>
       <c r="B37" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>21</v>
@@ -2746,10 +2759,10 @@
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="23"/>
       <c r="B38" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>21</v>
@@ -2758,7 +2771,7 @@
         <v>13</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>14</v>
@@ -2775,10 +2788,10 @@
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="23"/>
       <c r="B39" s="26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D39" s="27"/>
       <c r="E39" s="27" t="s">
@@ -2803,16 +2816,16 @@
       </c>
       <c r="K39" s="27"/>
       <c r="L39" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="23"/>
       <c r="B40" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D40" s="27"/>
       <c r="E40" s="27" t="s">
@@ -2822,7 +2835,7 @@
         <v>13</v>
       </c>
       <c r="G40" s="27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H40" s="27" t="s">
         <v>14</v>
@@ -2840,10 +2853,10 @@
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="23"/>
       <c r="B41" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>21</v>
@@ -2852,7 +2865,7 @@
         <v>25</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>14</v>
@@ -2869,10 +2882,10 @@
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="23"/>
       <c r="B42" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>17</v>
@@ -2881,7 +2894,7 @@
         <v>25</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J42" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G42)</f>
@@ -2891,10 +2904,10 @@
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="23"/>
       <c r="B43" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>17</v>
@@ -2903,7 +2916,7 @@
         <v>25</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J43" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G43)</f>
@@ -2913,10 +2926,10 @@
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="23"/>
       <c r="B44" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>17</v>
@@ -2925,7 +2938,7 @@
         <v>25</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J44" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G44)</f>
@@ -2935,10 +2948,10 @@
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="23"/>
       <c r="B45" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>17</v>
@@ -2947,7 +2960,7 @@
         <v>25</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J45" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G45)</f>
@@ -2957,10 +2970,10 @@
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="23"/>
       <c r="B46" s="10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>17</v>
@@ -2969,7 +2982,7 @@
         <v>25</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J46" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G46)</f>
@@ -2979,10 +2992,10 @@
     <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="23"/>
       <c r="B47" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>17</v>
@@ -2991,7 +3004,7 @@
         <v>25</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>14</v>
@@ -3011,7 +3024,7 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="4"/>
@@ -3035,10 +3048,10 @@
     <row r="49" customFormat="false" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7"/>
       <c r="B49" s="10" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>17</v>
@@ -3064,10 +3077,10 @@
     <row r="50" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
       <c r="B50" s="10" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>21</v>
@@ -3093,10 +3106,10 @@
     <row r="51" customFormat="false" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
       <c r="B51" s="10" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E51" s="24" t="s">
         <v>50</v>
@@ -3122,10 +3135,10 @@
     <row r="52" customFormat="false" ht="46" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7"/>
       <c r="B52" s="10" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>21</v>
@@ -3134,7 +3147,7 @@
         <v>25</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>14</v>
@@ -3151,10 +3164,10 @@
     <row r="53" customFormat="false" ht="46" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7"/>
       <c r="B53" s="10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>21</v>
@@ -3163,7 +3176,7 @@
         <v>25</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>14</v>
@@ -3179,11 +3192,11 @@
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="32" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="22" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D54" s="22"/>
       <c r="E54" s="21"/>
@@ -3210,7 +3223,7 @@
         <v>17</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E55" s="13" t="s">
         <v>17</v>
@@ -3236,19 +3249,19 @@
     <row r="56" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="33"/>
       <c r="B56" s="14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H56" s="13" t="s">
         <v>14</v>
@@ -3265,10 +3278,10 @@
     <row r="57" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="33"/>
       <c r="B57" s="14" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E57" s="13" t="s">
         <v>21</v>
@@ -3294,10 +3307,10 @@
     <row r="58" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="33"/>
       <c r="B58" s="14" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E58" s="13" t="s">
         <v>21</v>
@@ -3323,10 +3336,10 @@
     <row r="59" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="33"/>
       <c r="B59" s="14" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E59" s="13" t="s">
         <v>21</v>
@@ -3335,7 +3348,7 @@
         <v>25</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H59" s="13" t="s">
         <v>14</v>
@@ -3352,19 +3365,19 @@
     <row r="60" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="33"/>
       <c r="B60" s="14" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F60" s="13" t="s">
         <v>51</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H60" s="13" t="s">
         <v>14</v>
@@ -3380,20 +3393,20 @@
     </row>
     <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I61" s="5" t="str">
         <f aca="false">_xlfn.CONCAT(H61, G61)</f>
@@ -3404,7 +3417,7 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#System</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3413,7 +3426,7 @@
         <v>17</v>
       </c>
       <c r="C62" s="35" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="D62" s="35"/>
       <c r="G62" s="13" t="s">
@@ -3434,7 +3447,7 @@
     <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7"/>
       <c r="B63" s="10" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C63" s="35"/>
       <c r="D63" s="35"/>
@@ -3456,7 +3469,7 @@
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7"/>
       <c r="B64" s="10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C64" s="35"/>
       <c r="D64" s="35"/>
@@ -3478,14 +3491,14 @@
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7"/>
       <c r="B65" s="10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C65" s="35" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D65" s="35"/>
       <c r="G65" s="35" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J65" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G65)</f>
@@ -3495,18 +3508,18 @@
     <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7"/>
       <c r="B66" s="10" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C66" s="35"/>
       <c r="D66" s="35"/>
       <c r="E66" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I66" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H66, G66)</f>
@@ -3520,18 +3533,18 @@
     <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7"/>
       <c r="B67" s="10" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C67" s="35"/>
       <c r="D67" s="35"/>
       <c r="E67" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I67" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H67, G67)</f>
@@ -3545,20 +3558,20 @@
     <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7"/>
       <c r="B68" s="10" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D68" s="35"/>
       <c r="E68" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G68" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="H68" s="35" t="s">
         <v>185</v>
-      </c>
-      <c r="G68" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="H68" s="35" t="s">
-        <v>182</v>
       </c>
       <c r="I68" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H68, G68)</f>
@@ -3583,7 +3596,7 @@
         <v>76</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I69" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H69, G69)</f>
@@ -3597,17 +3610,17 @@
     <row r="70" customFormat="false" ht="46" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7"/>
       <c r="B70" s="10" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D70" s="35"/>
       <c r="E70" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G70" s="35" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I70" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H70, G70)</f>
@@ -3621,17 +3634,17 @@
     <row r="71" customFormat="false" ht="46" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7"/>
       <c r="B71" s="10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C71" s="35" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D71" s="35"/>
       <c r="E71" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G71" s="35" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I71" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H71, G71)</f>
@@ -3645,13 +3658,13 @@
     <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7"/>
       <c r="B72" s="10" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="J72" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G72)</f>
@@ -3661,14 +3674,14 @@
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7"/>
       <c r="B73" s="10" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C73" s="35" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D73" s="35"/>
       <c r="E73" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G73" s="35"/>
       <c r="J73" s="1" t="str">
@@ -3679,7 +3692,7 @@
     <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7"/>
       <c r="B74" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="J74" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G74)</f>
@@ -3689,7 +3702,7 @@
     <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7"/>
       <c r="B75" s="10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J75" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G75)</f>
@@ -3699,7 +3712,7 @@
     <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7"/>
       <c r="B76" s="10" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J76" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G76)</f>
@@ -3709,7 +3722,7 @@
     <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7"/>
       <c r="B77" s="10" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J77" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G77)</f>
@@ -3719,7 +3732,7 @@
     <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7"/>
       <c r="B78" s="10" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J78" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G78)</f>
@@ -3729,7 +3742,7 @@
     <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7"/>
       <c r="B79" s="10" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J79" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G79)</f>
@@ -3739,7 +3752,7 @@
     <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7"/>
       <c r="B80" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J80" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G80)</f>
@@ -3749,7 +3762,7 @@
     <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7"/>
       <c r="B81" s="10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="J81" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G81)</f>
@@ -3759,7 +3772,7 @@
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7"/>
       <c r="B82" s="10" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="J82" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G82)</f>
@@ -3769,7 +3782,7 @@
     <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7"/>
       <c r="B83" s="10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J83" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G83)</f>
@@ -3778,20 +3791,20 @@
     </row>
     <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="32" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B84" s="21"/>
       <c r="C84" s="22" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D84" s="22"/>
       <c r="E84" s="21"/>
       <c r="F84" s="21"/>
       <c r="G84" s="21" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H84" s="22" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I84" s="22" t="str">
         <f aca="false">_xlfn.CONCAT(H84, G84)</f>
@@ -3806,10 +3819,10 @@
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="23"/>
       <c r="B85" s="10" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>18</v>
@@ -3829,7 +3842,7 @@
     <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="23"/>
       <c r="B86" s="10" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>22</v>
@@ -3849,7 +3862,7 @@
     <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="23"/>
       <c r="B87" s="10" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>26</v>
@@ -3869,10 +3882,10 @@
     <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="23"/>
       <c r="B88" s="10" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J88" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G88)</f>
@@ -3882,10 +3895,10 @@
     <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="23"/>
       <c r="B89" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J89" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G89)</f>
@@ -3895,7 +3908,7 @@
     <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="23"/>
       <c r="B90" s="10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>39</v>
@@ -3915,7 +3928,7 @@
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="23"/>
       <c r="B91" s="10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>52</v>
@@ -3927,20 +3940,20 @@
     </row>
     <row r="92" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="25" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
       <c r="G92" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I92" s="5" t="str">
         <f aca="false">_xlfn.CONCAT(H92, G92)</f>
@@ -3955,10 +3968,10 @@
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7"/>
       <c r="B93" s="10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>18</v>
@@ -3978,7 +3991,7 @@
     <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7"/>
       <c r="B94" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>22</v>
@@ -3998,7 +4011,7 @@
     <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7"/>
       <c r="B95" s="10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>26</v>
@@ -4018,10 +4031,10 @@
     <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7"/>
       <c r="B96" s="10" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J96" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G96)</f>
@@ -4031,10 +4044,10 @@
     <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7"/>
       <c r="B97" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J97" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G97)</f>
@@ -4044,7 +4057,7 @@
     <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7"/>
       <c r="B98" s="10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>39</v>
@@ -4064,13 +4077,13 @@
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7"/>
       <c r="B99" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I99" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(H99, G99)</f>
@@ -4084,7 +4097,7 @@
     <row r="100" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7"/>
       <c r="B100" s="10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>52</v>
@@ -4096,20 +4109,20 @@
     </row>
     <row r="101" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="32" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B101" s="21"/>
       <c r="C101" s="22" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D101" s="22"/>
       <c r="E101" s="21"/>
       <c r="F101" s="21"/>
       <c r="G101" s="21" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H101" s="22" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I101" s="22" t="str">
         <f aca="false">_xlfn.CONCAT(H101, G101)</f>
@@ -4120,7 +4133,7 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#Observation </v>
       </c>
       <c r="K101" s="21" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4129,7 +4142,7 @@
         <v>17</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>18</v>
@@ -4142,10 +4155,10 @@
     <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="23"/>
       <c r="B103" s="10" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J103" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G103)</f>
@@ -4155,16 +4168,16 @@
     <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="23"/>
       <c r="B104" s="10" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J104" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G104)</f>
@@ -4174,13 +4187,13 @@
     <row r="105" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="23"/>
       <c r="B105" s="10" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J105" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G105)</f>
@@ -4190,10 +4203,10 @@
     <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="23"/>
       <c r="B106" s="10" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>52</v>
@@ -4206,13 +4219,13 @@
     <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="23"/>
       <c r="B107" s="10" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J107" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G107)</f>
@@ -4221,17 +4234,17 @@
     </row>
     <row r="108" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="25" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="5" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D108" s="5"/>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="G108" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H108" s="5" t="s">
         <v>14</v>
@@ -4252,7 +4265,7 @@
         <v>17</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>18</v>
@@ -4272,16 +4285,16 @@
     <row r="110" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7"/>
       <c r="B110" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>51</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H110" s="11" t="s">
         <v>14</v>
@@ -4298,10 +4311,10 @@
     <row r="111" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7"/>
       <c r="B111" s="10" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J111" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G111)</f>
@@ -4311,7 +4324,7 @@
     <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7"/>
       <c r="B112" s="10" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>26</v>
@@ -4331,10 +4344,10 @@
     <row r="113" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7"/>
       <c r="B113" s="10" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H113" s="11" t="s">
         <v>14</v>
@@ -4351,14 +4364,14 @@
     <row r="114" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7"/>
       <c r="B114" s="26" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C114" s="27"/>
       <c r="D114" s="27"/>
       <c r="E114" s="27"/>
       <c r="F114" s="27"/>
       <c r="G114" s="27" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H114" s="27" t="s">
         <v>14</v>
@@ -4373,20 +4386,20 @@
       </c>
       <c r="K114" s="27"/>
       <c r="L114" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7"/>
       <c r="B115" s="26" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C115" s="27"/>
       <c r="D115" s="27"/>
       <c r="E115" s="27"/>
       <c r="F115" s="27"/>
       <c r="G115" s="27" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H115" s="27" t="s">
         <v>14</v>
@@ -4404,10 +4417,10 @@
     <row r="116" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7"/>
       <c r="B116" s="10" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H116" s="11" t="s">
         <v>14</v>
@@ -4424,7 +4437,7 @@
     <row r="117" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7"/>
       <c r="B117" s="10" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H117" s="11" t="s">
         <v>14</v>
@@ -4440,17 +4453,17 @@
     </row>
     <row r="118" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="32" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B118" s="21"/>
       <c r="C118" s="22" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D118" s="22"/>
       <c r="E118" s="21"/>
       <c r="F118" s="21"/>
       <c r="G118" s="21" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H118" s="22" t="s">
         <v>14</v>
@@ -4464,16 +4477,16 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#ObservedVariable</v>
       </c>
       <c r="K118" s="21" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="23"/>
       <c r="B119" s="10" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>18</v>
@@ -4489,7 +4502,7 @@
     <row r="120" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="23"/>
       <c r="B120" s="10" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H120" s="11" t="s">
         <v>14</v>
@@ -4502,7 +4515,7 @@
     <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="23"/>
       <c r="B121" s="10" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="J121" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G121)</f>
@@ -4512,7 +4525,7 @@
     <row r="122" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="23"/>
       <c r="B122" s="10" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J122" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G122)</f>
@@ -4522,13 +4535,13 @@
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="23"/>
       <c r="B123" s="10" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="23"/>
       <c r="B124" s="10" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4545,17 +4558,17 @@
     </row>
     <row r="127" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="25" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D127" s="5"/>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
       <c r="G127" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H127" s="5" t="s">
         <v>14</v>
@@ -4576,7 +4589,7 @@
         <v>17</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>18</v>
@@ -4592,10 +4605,10 @@
     <row r="129" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7"/>
       <c r="B129" s="10" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J129" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G129)</f>
@@ -4605,7 +4618,7 @@
     <row r="130" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7"/>
       <c r="B130" s="10" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J130" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G130)</f>
@@ -4615,37 +4628,37 @@
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7"/>
       <c r="B131" s="10" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7"/>
       <c r="B132" s="10" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7"/>
       <c r="B133" s="10" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="32" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B134" s="21"/>
       <c r="C134" s="22" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D134" s="22"/>
       <c r="E134" s="21"/>
       <c r="F134" s="21"/>
       <c r="G134" s="21" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="H134" s="22" t="s">
         <v>14</v>
@@ -4663,7 +4676,7 @@
         <v>17</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>18</v>
@@ -4691,17 +4704,17 @@
     </row>
     <row r="138" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="25" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="5" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D138" s="5"/>
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
       <c r="G138" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H138" s="5" t="s">
         <v>14</v>
@@ -4716,10 +4729,10 @@
     <row r="139" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7"/>
       <c r="B139" s="10" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>18</v>
@@ -4735,10 +4748,10 @@
     <row r="140" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7"/>
       <c r="B140" s="10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J140" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G140)</f>
@@ -4748,28 +4761,28 @@
     <row r="141" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7"/>
       <c r="B141" s="10" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7"/>
       <c r="B142" s="10" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7"/>
       <c r="B143" s="10" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7"/>
       <c r="B144" s="10" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4806,17 +4819,17 @@
     </row>
     <row r="153" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="32" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B153" s="21"/>
       <c r="C153" s="22" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D153" s="22"/>
       <c r="E153" s="21"/>
       <c r="F153" s="21"/>
       <c r="G153" s="21" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H153" s="22" t="s">
         <v>14</v>
@@ -4834,7 +4847,7 @@
         <v>17</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>18</v>
@@ -4873,11 +4886,11 @@
     </row>
     <row r="158" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D158" s="5"/>
       <c r="E158" s="4"/>
@@ -4899,7 +4912,7 @@
         <v>17</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>18</v>
@@ -4918,34 +4931,34 @@
         <v>53</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H160" s="11" t="s">
         <v>14</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7"/>
       <c r="B161" s="10" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H161" s="11" t="s">
         <v>14</v>
@@ -4958,16 +4971,16 @@
     <row r="162" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7"/>
       <c r="B162" s="10" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H162" s="11" t="s">
         <v>14</v>
@@ -4976,13 +4989,13 @@
     <row r="163" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7"/>
       <c r="B163" s="10" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>51</v>
@@ -4994,13 +5007,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="35.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="32" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B164" s="21"/>
       <c r="C164" s="22" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D164" s="22"/>
       <c r="E164" s="21"/>
@@ -5008,7 +5021,7 @@
         <v>55</v>
       </c>
       <c r="G164" s="21" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H164" s="22" t="s">
         <v>14</v>
@@ -5023,10 +5036,10 @@
     <row r="165" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="23"/>
       <c r="B165" s="10" t="s">
-        <v>17</v>
+        <v>303</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E165" s="30" t="s">
         <v>17</v>
@@ -5048,10 +5061,10 @@
     <row r="166" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="23"/>
       <c r="B166" s="10" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E166" s="30" t="s">
         <v>21</v>
@@ -5073,10 +5086,10 @@
     <row r="167" s="30" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="23"/>
       <c r="B167" s="10" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E167" s="30" t="s">
         <v>17</v>
@@ -5085,7 +5098,7 @@
         <v>51</v>
       </c>
       <c r="G167" s="30" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="H167" s="36" t="s">
         <v>14</v>
@@ -5098,10 +5111,10 @@
     <row r="168" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="23"/>
       <c r="B168" s="10" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D168" s="30"/>
       <c r="E168" s="1" t="s">
@@ -5111,7 +5124,7 @@
         <v>51</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="H168" s="11" t="s">
         <v>14</v>
@@ -5124,19 +5137,19 @@
     <row r="169" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="23"/>
       <c r="B169" s="10" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E169" s="24" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>51</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H169" s="11" t="s">
         <v>14</v>
@@ -5149,10 +5162,10 @@
     <row r="170" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="23"/>
       <c r="B170" s="10" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E170" s="24" t="s">
         <v>72</v>
@@ -5161,7 +5174,7 @@
         <v>55</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H170" s="11" t="s">
         <v>14</v>
@@ -5173,11 +5186,11 @@
     </row>
     <row r="171" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="37" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B171" s="38"/>
       <c r="C171" s="39" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D171" s="39"/>
       <c r="E171" s="38"/>
@@ -5190,7 +5203,7 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
       <c r="K171" s="38" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="172" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5199,7 +5212,7 @@
         <v>17</v>
       </c>
       <c r="C172" s="13" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="J172" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G172)</f>
@@ -5209,7 +5222,7 @@
     <row r="173" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="40"/>
       <c r="B173" s="14" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J173" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G173)</f>
@@ -5219,7 +5232,7 @@
     <row r="174" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="40"/>
       <c r="B174" s="14" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="J174" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G174)</f>
@@ -5229,7 +5242,7 @@
     <row r="175" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="40"/>
       <c r="B175" s="14" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J175" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G175)</f>
@@ -5239,7 +5252,7 @@
     <row r="176" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="40"/>
       <c r="B176" s="14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J176" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G176)</f>
@@ -5249,7 +5262,7 @@
     <row r="177" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="40"/>
       <c r="B177" s="14" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="J177" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G177)</f>
@@ -5259,10 +5272,10 @@
     <row r="178" s="13" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="40"/>
       <c r="B178" s="14" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E178" s="13" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="J178" s="1" t="str">
         <f aca="false">_xlfn.CONCAT("https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#", G178)</f>
@@ -5271,11 +5284,11 @@
     </row>
     <row r="179" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="37" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B179" s="38"/>
       <c r="C179" s="39" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D179" s="39"/>
       <c r="E179" s="38"/>
@@ -5288,7 +5301,7 @@
         <v>https://github.com/gryvity/miafpe/tree/master/ontology/miappexsosa.owl#</v>
       </c>
       <c r="K179" s="38" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5297,7 +5310,7 @@
         <v>17</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>18</v>
@@ -5326,9 +5339,28 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF81D41A"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J2"/>
@@ -5376,18 +5408,18 @@
         <v>44</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" s="35" customFormat="true" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D2" s="42" t="n">
         <v>45644</v>
@@ -5396,7 +5428,7 @@
         <v>45644</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G2" s="35" t="n">
         <v>3.2</v>
@@ -5419,6 +5451,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF81D41A"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I1"/>
@@ -5482,7 +5515,7 @@
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="24.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="14.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="19.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="14.94"/>
@@ -5494,22 +5527,22 @@
   <sheetData>
     <row r="1" s="41" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="41" t="s">
-        <v>17</v>
+        <v>303</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -5546,19 +5579,19 @@
         <v>17</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D1" s="43" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F1" s="43" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -5595,31 +5628,31 @@
         <v>17</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -5656,37 +5689,37 @@
         <v>17</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D1" s="43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F1" s="43" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G1" s="43" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H1" s="43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I1" s="43" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J1" s="43" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K1" s="43" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L1" s="43" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -5720,19 +5753,19 @@
   <sheetData>
     <row r="1" s="41" customFormat="true" ht="36.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="43" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D1" s="43" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -5744,4 +5777,22 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>